--- a/周汇总表.xlsx
+++ b/周汇总表.xlsx
@@ -163,17 +163,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>W16[0413-0419]</t>
+          <t>W17[0420-0426]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>20231011000001</t>
+          <t>20220426000001</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>深圳中心仓</t>
+          <t>转转-青岛智能验机中心</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -188,47 +188,47 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1346</t>
+          <t>1212</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>1047</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>165</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4.68%</t>
+          <t>13.61%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2.82%</t>
+          <t>0.91%</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>158</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2.01%</t>
+          <t>13.04%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>4.83%</t>
+          <t>13.94%</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -248,89 +248,89 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1346</t>
+          <t>1212</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>11</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2.82%</t>
+          <t>0.91%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>W16[0413-0419]</t>
+          <t>W17[0420-0426]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>杭州库</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>手机</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>818</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>781</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4.52%</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2.69%</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>南昌库</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>手机</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>739</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>720</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2.57%</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>1.76%</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>0.81%</t>
+          <t>1.96%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2.57%</t>
+          <t>4.65%</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -350,34 +350,34 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>739</t>
+          <t>818</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>22</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1.76%</t>
+          <t>2.69%</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>W16[0413-0419]</t>
+          <t>W17[0420-0426]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>杭州库</t>
+          <t>福州库</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -392,47 +392,47 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>801</t>
+          <t>217</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>761</t>
+          <t>208</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4.99%</t>
+          <t>4.15%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1.87%</t>
+          <t>3.23%</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>3.12%</t>
+          <t>0.92%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>4.99%</t>
+          <t>4.15%</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -452,34 +452,34 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>801</t>
+          <t>217</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1.87%</t>
+          <t>3.23%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>W16[0413-0419]</t>
+          <t>W17[0420-0426]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>昆明库</t>
+          <t>南京库</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -494,47 +494,47 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>477</t>
+          <t>1031</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>976</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>55</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4.61%</t>
+          <t>5.33%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>4.36%</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>2.31%</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2.31%</t>
+          <t>1.07%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>4.61%</t>
+          <t>5.43%</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -554,34 +554,34 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>477</t>
+          <t>1031</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>45</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2.31%</t>
+          <t>4.36%</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>W16[0413-0419]</t>
+          <t>W17[0420-0426]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>20250828000002</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>青岛后验中心仓</t>
+          <t>武汉库</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -596,47 +596,47 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>1024</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>1009</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>7.83%</t>
+          <t>1.46%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>3.48%</t>
+          <t>0.88%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>4.35%</t>
+          <t>0.59%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>7.83%</t>
+          <t>1.46%</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -656,34 +656,34 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>1024</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>3.48%</t>
+          <t>0.88%</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>W16[0413-0419]</t>
+          <t>W17[0420-0426]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20230613000001</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>沈阳库</t>
+          <t>深圳后验中心仓</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -698,94 +698,94 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>233</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>224</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>6.06%</t>
+          <t>3.86%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>5.1%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>1.29%</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>4.29%</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>1.12%</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>6.22%</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>627</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>5.10%</t>
+          <t>3.00%</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>W16[0413-0419]</t>
+          <t>W17[0420-0426]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>郑州库</t>
+          <t>重庆库</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -800,32 +800,32 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>928</t>
+          <t>837</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>892</t>
+          <t>812</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3.88%</t>
+          <t>2.99%</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>3.23%</t>
+          <t>2.27%</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -835,12 +835,12 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>0.65%</t>
+          <t>0.72%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>3.88%</t>
+          <t>2.99%</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -860,34 +860,34 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>928</t>
+          <t>837</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>19</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>3.23%</t>
+          <t>2.27%</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>W16[0413-0419]</t>
+          <t>W17[0420-0426]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>石家庄库</t>
+          <t>昆明库</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -902,32 +902,32 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>860</t>
+          <t>481</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>828</t>
+          <t>456</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3.72%</t>
+          <t>5.2%</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2.09%</t>
+          <t>2.08%</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -937,12 +937,12 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>1.86%</t>
+          <t>3.33%</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>3.95%</t>
+          <t>5.41%</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -962,34 +962,34 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>860</t>
+          <t>481</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>10</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2.09%</t>
+          <t>2.08%</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>W16[0413-0419]</t>
+          <t>W17[0420-0426]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>20240312000001</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>转转-深圳智能验机中心</t>
+          <t>长沙库</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1004,47 +1004,47 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1216</t>
+          <t>955</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1044</t>
+          <t>921</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>14.14%</t>
+          <t>3.56%</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>12</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>12.99%</t>
+          <t>1.26%</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>14.39%</t>
+          <t>3.56%</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1064,34 +1064,34 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1216</t>
+          <t>955</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>22</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1.40%</t>
+          <t>2.30%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>W16[0413-0419]</t>
+          <t>W17[0420-0426]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20231122000001</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>西安库</t>
+          <t>襄阳中心仓</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1106,47 +1106,47 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>802</t>
+          <t>946</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>785</t>
+          <t>931</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2.12%</t>
+          <t>1.59%</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>1.37%</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>0.21%</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2.12%</t>
+          <t>1.59%</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1166,24 +1166,24 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>802</t>
+          <t>946</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1.50%</t>
+          <t>1.37%</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>W16[0413-0419]</t>
+          <t>W17[0420-0426]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1208,47 +1208,47 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1202</t>
+          <t>1208</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>990</t>
+          <t>1006</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>202</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>17.64%</t>
+          <t>16.72%</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1.33%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>197</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>16.64%</t>
+          <t>16.31%</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>17.97%</t>
+          <t>17.05%</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1268,34 +1268,34 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1202</t>
+          <t>1208</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>9</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1.33%</t>
+          <t>0.75%</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>W16[0413-0419]</t>
+          <t>W17[0420-0426]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>合肥库</t>
+          <t>石家庄库</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1310,47 +1310,47 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>839</t>
+          <t>874</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>782</t>
+          <t>844</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>6.79%</t>
+          <t>3.43%</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2.74%</t>
+          <t>2.06%</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>12</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>4.17%</t>
+          <t>1.37%</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>6.91%</t>
+          <t>3.43%</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1370,34 +1370,34 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>839</t>
+          <t>874</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>18</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2.74%</t>
+          <t>2.06%</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>W16[0413-0419]</t>
+          <t>W17[0420-0426]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20240312000001</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>重庆库</t>
+          <t>转转-深圳智能验机中心</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1412,47 +1412,47 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>782</t>
+          <t>1212</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>751</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>189</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3.96%</t>
+          <t>15.59%</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2.94%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>177</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>1.02%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>3.96%</t>
+          <t>16.01%</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1472,34 +1472,34 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>782</t>
+          <t>1212</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>17</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2.94%</t>
+          <t>1.40%</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>W16[0413-0419]</t>
+          <t>W17[0420-0426]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>20231122000001</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>襄阳中心仓</t>
+          <t>合肥库</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1514,47 +1514,47 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>935</t>
+          <t>858</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>896</t>
+          <t>813</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>45</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>4.17%</t>
+          <t>5.24%</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2.14%</t>
+          <t>1.98%</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>28</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2.03%</t>
+          <t>3.26%</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>4.17%</t>
+          <t>5.24%</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1574,34 +1574,34 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>935</t>
+          <t>858</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2.14%</t>
+          <t>1.98%</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>W16[0413-0419]</t>
+          <t>W17[0420-0426]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>成都库</t>
+          <t>济南库</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1616,47 +1616,47 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1167</t>
+          <t>898</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1111</t>
+          <t>858</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>40</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>4.45%</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2.66%</t>
+          <t>2.34%</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>19</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2.31%</t>
+          <t>2.12%</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>4.97%</t>
+          <t>4.45%</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1167</t>
+          <t>898</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>21</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2.66%</t>
+          <t>2.34%</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>W16[0413-0419]</t>
+          <t>W17[0420-0426]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>武汉库</t>
+          <t>郑州库</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1718,47 +1718,47 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>855</t>
+          <t>912</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>834</t>
+          <t>873</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.46%</t>
+          <t>4.28%</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2.11%</t>
+          <t>3.18%</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2.46%</t>
+          <t>4.28%</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1778,34 +1778,34 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>855</t>
+          <t>912</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>29</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2.11%</t>
+          <t>3.18%</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>W16[0413-0419]</t>
+          <t>W17[0420-0426]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>20220426000001</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>转转-青岛智能验机中心</t>
+          <t>沈阳库</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1820,47 +1820,47 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1205</t>
+          <t>541</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1032</t>
+          <t>524</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>14.36%</t>
+          <t>3.14%</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>1.0%</t>
+          <t>2.77%</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>13.78%</t>
+          <t>0.37%</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>14.77%</t>
+          <t>3.14%</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -1880,34 +1880,34 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1205</t>
+          <t>541</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>2.77%</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>W16[0413-0419]</t>
+          <t>W17[0420-0426]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>长沙库</t>
+          <t>成都库</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1922,47 +1922,47 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>1160</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>919</t>
+          <t>1086</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>74</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3.87%</t>
+          <t>6.38%</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>45</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>1.88%</t>
+          <t>3.88%</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>29</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>1.99%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>3.87%</t>
+          <t>6.38%</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -1982,89 +1982,89 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>1160</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>45</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1.88%</t>
+          <t>3.88%</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>W16[0413-0419]</t>
+          <t>W17[0420-0426]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
+          <t>20250828000002</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>青岛后验中心仓</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>手机</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>济南库</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>手机</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>1035</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>984</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>4.93%</t>
+          <t>5.25%</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2.61%</t>
+          <t>2.16%</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2.32%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>4.93%</t>
+          <t>5.56%</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -2084,34 +2084,34 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1035</t>
+          <t>324</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>7</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2.61%</t>
+          <t>2.16%</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>W16[0413-0419]</t>
+          <t>W17[0420-0426]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>南京库</t>
+          <t>西安库</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2126,47 +2126,47 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>894</t>
+          <t>884</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>819</t>
+          <t>868</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>8.39%</t>
+          <t>1.81%</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>4.25%</t>
+          <t>1.58%</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>4.36%</t>
+          <t>0.23%</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>8.61%</t>
+          <t>1.81%</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2186,34 +2186,34 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>894</t>
+          <t>884</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>14</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>4.25%</t>
+          <t>1.58%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>W16[0413-0419]</t>
+          <t>W17[0420-0426]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>20230613000001</t>
+          <t>20231011000001</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>深圳后验中心仓</t>
+          <t>深圳中心仓</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2228,47 +2228,47 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>1317</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>1241</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>76</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>5.06%</t>
+          <t>5.77%</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>55</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>1.69%</t>
+          <t>4.18%</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>24</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>3.38%</t>
+          <t>1.82%</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>5.06%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2288,17 +2288,119 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>1317</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>55</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1.69%</t>
+          <t>4.18%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>W17[0420-0426]</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>南昌库</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>手机</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>653</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>4.29%</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2.14%</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2.3%</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>4.44%</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>653</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>2.14%</t>
         </is>
       </c>
     </row>

--- a/周汇总表.xlsx
+++ b/周汇总表.xlsx
@@ -163,17 +163,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>W18[0427-0503]</t>
+          <t>W19[0504-0510]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20230613000001</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>南昌库</t>
+          <t>深圳后验中心仓</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -188,47 +188,47 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>277</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>583</t>
+          <t>265</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2.35%</t>
+          <t>4.33%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1.17%</t>
+          <t>1.81%</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>1.17%</t>
+          <t>2.89%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2.35%</t>
+          <t>4.69%</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -248,34 +248,34 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>277</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1.17%</t>
+          <t>1.81%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>W18[0427-0503]</t>
+          <t>W19[0504-0510]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>郑州库</t>
+          <t>济南库</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -290,47 +290,47 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>859</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>820</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2.83%</t>
+          <t>4.54%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1.62%</t>
+          <t>2.33%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>22</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>1.21%</t>
+          <t>2.56%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2.83%</t>
+          <t>4.89%</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -350,34 +350,34 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>859</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1.62%</t>
+          <t>2.33%</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>W18[0427-0503]</t>
+          <t>W19[0504-0510]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>济南库</t>
+          <t>郑州库</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -392,47 +392,47 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>518</t>
+          <t>965</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>937</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3.67%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2.12%</t>
+          <t>2.28%</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>1.54%</t>
+          <t>0.62%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>3.67%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -452,34 +452,34 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>518</t>
+          <t>965</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>22</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2.12%</t>
+          <t>2.28%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>W18[0427-0503]</t>
+          <t>W19[0504-0510]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>长沙库</t>
+          <t>沈阳库</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -494,32 +494,32 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>797</t>
+          <t>1007</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>766</t>
+          <t>960</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>47</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3.89%</t>
+          <t>4.67%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1.51%</t>
+          <t>2.88%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -529,12 +529,12 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2.51%</t>
+          <t>1.99%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>4.02%</t>
+          <t>4.87%</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -554,34 +554,34 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>797</t>
+          <t>1007</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>29</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1.51%</t>
+          <t>2.88%</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>W18[0427-0503]</t>
+          <t>W19[0504-0510]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>武汉库</t>
+          <t>西安库</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -596,47 +596,47 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>796</t>
+          <t>810</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>774</t>
+          <t>772</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>38</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2.76%</t>
+          <t>4.69%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>1.63%</t>
+          <t>2.84%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>1.13%</t>
+          <t>1.98%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2.76%</t>
+          <t>4.81%</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -656,34 +656,34 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>796</t>
+          <t>810</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>23</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1.63%</t>
+          <t>2.84%</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>W18[0427-0503]</t>
+          <t>W19[0504-0510]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>50759535847188</t>
+          <t>20220426000001</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>转转-成都智能验机中心</t>
+          <t>转转-青岛智能验机中心</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -698,47 +698,47 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1025</t>
+          <t>1203</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>840</t>
+          <t>989</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>214</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>18.05%</t>
+          <t>17.79%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.78%</t>
+          <t>1.41%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>202</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>17.37%</t>
+          <t>16.79%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>18.15%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -758,34 +758,34 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1025</t>
+          <t>1203</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>17</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.78%</t>
+          <t>1.41%</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>W18[0427-0503]</t>
+          <t>W19[0504-0510]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>20240312000001</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>转转-深圳智能验机中心</t>
+          <t>石家庄库</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -800,47 +800,47 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1060</t>
+          <t>788</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>878</t>
+          <t>765</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>17.17%</t>
+          <t>2.92%</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>1.98%</t>
+          <t>1.65%</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>15.66%</t>
+          <t>1.27%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>17.64%</t>
+          <t>2.92%</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -860,34 +860,34 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1060</t>
+          <t>788</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>13</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1.98%</t>
+          <t>1.65%</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>W18[0427-0503]</t>
+          <t>W19[0504-0510]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20240312000001</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>南京库</t>
+          <t>转转-深圳智能验机中心</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -902,47 +902,47 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>736</t>
+          <t>1218</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>696</t>
+          <t>986</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>232</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5.43%</t>
+          <t>19.05%</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2.99%</t>
+          <t>1.72%</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>215</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2.72%</t>
+          <t>17.65%</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>5.71%</t>
+          <t>19.38%</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -962,34 +962,34 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>736</t>
+          <t>1218</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2.99%</t>
+          <t>1.72%</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>W18[0427-0503]</t>
+          <t>W19[0504-0510]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>20231011000001</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>深圳中心仓</t>
+          <t>杭州库</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1004,47 +1004,47 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1017</t>
+          <t>831</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>963</t>
+          <t>797</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5.31%</t>
+          <t>4.09%</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>3.24%</t>
+          <t>1.93%</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2.16%</t>
+          <t>2.17%</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>5.41%</t>
+          <t>4.09%</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1064,34 +1064,34 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1017</t>
+          <t>831</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>16</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>3.24%</t>
+          <t>1.93%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>W18[0427-0503]</t>
+          <t>W19[0504-0510]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>沈阳库</t>
+          <t>昆明库</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1106,47 +1106,47 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>739</t>
+          <t>390</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>705</t>
+          <t>376</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4.6%</t>
+          <t>3.59%</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>3.38%</t>
+          <t>1.79%</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1.35%</t>
+          <t>1.79%</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>4.74%</t>
+          <t>3.59%</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1166,34 +1166,34 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>739</t>
+          <t>390</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>7</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>3.38%</t>
+          <t>1.79%</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>W18[0427-0503]</t>
+          <t>W19[0504-0510]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>重庆库</t>
+          <t>合肥库</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1208,47 +1208,47 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>623</t>
+          <t>898</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>803</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>95</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5.62%</t>
+          <t>10.58%</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>3.21%</t>
+          <t>3.01%</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>70</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2.41%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>5.62%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1268,34 +1268,34 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>623</t>
+          <t>898</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>27</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>3.21%</t>
+          <t>3.01%</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>W18[0427-0503]</t>
+          <t>W19[0504-0510]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>成都库</t>
+          <t>南京库</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1310,47 +1310,47 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>1241</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>703</t>
+          <t>1179</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>62</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>6.76%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>46</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>4.38%</t>
+          <t>3.71%</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2.52%</t>
+          <t>1.29%</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1370,34 +1370,34 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>1241</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>46</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>4.38%</t>
+          <t>3.71%</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>W18[0427-0503]</t>
+          <t>W19[0504-0510]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>20231122000001</t>
+          <t>50759535847188</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>襄阳中心仓</t>
+          <t>转转-成都智能验机中心</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1412,47 +1412,47 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>1213</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>775</t>
+          <t>974</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>239</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.88%</t>
+          <t>19.7%</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1.75%</t>
+          <t>1.65%</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>224</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>1.38%</t>
+          <t>18.47%</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>3.13%</t>
+          <t>20.12%</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1472,34 +1472,34 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>1213</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>20</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1.75%</t>
+          <t>1.65%</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>W18[0427-0503]</t>
+          <t>W19[0504-0510]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>20220426000001</t>
+          <t>20231122000001</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>转转-青岛智能验机中心</t>
+          <t>襄阳中心仓</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1514,47 +1514,47 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1011</t>
+          <t>892</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>837</t>
+          <t>868</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>17.21%</t>
+          <t>2.69%</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>1.78%</t>
+          <t>1.46%</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>15.92%</t>
+          <t>1.23%</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>17.71%</t>
+          <t>2.69%</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1574,34 +1574,34 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1011</t>
+          <t>892</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>13</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1.78%</t>
+          <t>1.46%</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>W18[0427-0503]</t>
+          <t>W19[0504-0510]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>石家庄库</t>
+          <t>南昌库</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1616,47 +1616,47 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>652</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>591</t>
+          <t>640</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3.27%</t>
+          <t>1.84%</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>1.38%</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>1.64%</t>
+          <t>0.46%</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>3.44%</t>
+          <t>1.84%</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>652</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1.80%</t>
+          <t>1.38%</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>W18[0427-0503]</t>
+          <t>W19[0504-0510]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>20250828000002</t>
+          <t>20231011000001</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>青岛后验中心仓</t>
+          <t>深圳中心仓</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1718,47 +1718,47 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>1482</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>1412</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>70</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>7.61%</t>
+          <t>4.72%</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>41</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>4.35%</t>
+          <t>2.77%</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>30</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>2.02%</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>8.15%</t>
+          <t>4.79%</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1778,34 +1778,34 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>1482</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>41</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>4.35%</t>
+          <t>2.77%</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>W18[0427-0503]</t>
+          <t>W19[0504-0510]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>杭州库</t>
+          <t>成都库</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1820,47 +1820,47 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>795</t>
+          <t>1227</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>749</t>
+          <t>1161</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>66</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>5.79%</t>
+          <t>5.38%</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2.64%</t>
+          <t>3.26%</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>3.14%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>5.79%</t>
+          <t>5.46%</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -1880,89 +1880,89 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>795</t>
+          <t>1227</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>40</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2.64%</t>
+          <t>3.26%</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>W18[0427-0503]</t>
+          <t>W19[0504-0510]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>长沙库</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>手机</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>784</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>750</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>4.34%</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>昆明库</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>手机</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>554</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>539</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2.71%</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>1.62%</t>
+          <t>2.68%</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>1.08%</t>
+          <t>1.66%</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2.71%</t>
+          <t>4.34%</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -1982,34 +1982,34 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>554</t>
+          <t>784</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>21</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1.62%</t>
+          <t>2.68%</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>W18[0427-0503]</t>
+          <t>W19[0504-0510]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>合肥库</t>
+          <t>重庆库</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2024,47 +2024,47 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>797</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>768</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>6.78%</t>
+          <t>3.64%</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2.36%</t>
+          <t>2.63%</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>9</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>4.42%</t>
+          <t>1.13%</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>6.78%</t>
+          <t>3.76%</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -2084,34 +2084,34 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>797</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>21</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2.36%</t>
+          <t>2.63%</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>W18[0427-0503]</t>
+          <t>W19[0504-0510]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>20250828000002</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>福州库</t>
+          <t>青岛后验中心仓</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>374</t>
+          <t>385</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>371</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>5.08%</t>
+          <t>3.64%</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2151,22 +2151,22 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2.67%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2.41%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>5.08%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>374</t>
+          <t>385</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2196,24 +2196,24 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2.67%</t>
+          <t>2.60%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>W18[0427-0503]</t>
+          <t>W19[0504-0510]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>西安库</t>
+          <t>福州库</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2228,94 +2228,94 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>775</t>
+          <t>460</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>742</t>
+          <t>431</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>4.26%</t>
+          <t>6.3%</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2.32%</t>
+          <t>3.48%</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2.83%</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>6.3%</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>460</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>2.06%</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>4.39%</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>775</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2.32%</t>
+          <t>3.48%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>W18[0427-0503]</t>
+          <t>W19[0504-0510]</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>20230613000001</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>深圳后验中心仓</t>
+          <t>武汉库</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2330,47 +2330,47 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>785</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>761</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2.94%</t>
+          <t>3.06%</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2.52%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.42%</t>
+          <t>1.66%</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2.94%</t>
+          <t>3.06%</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2390,17 +2390,17 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>785</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2.52%</t>
+          <t>1.40%</t>
         </is>
       </c>
     </row>
